--- a/config/yunying/vipbuy.xlsx
+++ b/config/yunying/vipbuy.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="vipbuy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vipbuy" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1212,7 +1212,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1265,7 +1264,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1318,7 +1316,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1371,7 +1368,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1424,7 +1420,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1477,7 +1472,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1530,7 +1524,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1583,7 +1576,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1636,7 +1628,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1689,7 +1680,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1742,7 +1732,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1795,7 +1784,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1848,7 +1836,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1901,7 +1888,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>21001</t>
@@ -1954,7 +1940,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>21001</t>
@@ -2007,7 +1992,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>21001</t>
@@ -2060,17 +2044,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2095,7 +2069,7 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>VIP0パック</t>
+          <t>VIP0包</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2152,7 +2126,7 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>VIP1パック</t>
+          <t>VIP1包</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2209,7 +2183,7 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>VIP2パック</t>
+          <t>VIP2包</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2266,7 +2240,7 @@
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>VIP3パック</t>
+          <t>VIP3包</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2323,7 +2297,7 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>VIP4パック</t>
+          <t>VIP4包</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2380,7 +2354,7 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>VIP5パック</t>
+          <t>VIP5包</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2437,7 +2411,7 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>VIP6パック</t>
+          <t>VIP6包</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2494,7 +2468,7 @@
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>VIP7パック</t>
+          <t>VIP7包</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2551,7 +2525,7 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>VIP8パック</t>
+          <t>VIP8包</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2608,7 +2582,7 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>VIP9パック</t>
+          <t>VIP9包</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2665,7 +2639,7 @@
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>VIP10パック</t>
+          <t>VIP10包</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2722,7 +2696,7 @@
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>VIP11パック</t>
+          <t>VIP11包</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2779,7 +2753,7 @@
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>VIP12パック</t>
+          <t>VIP12包</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2836,7 +2810,7 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>VIP13パック</t>
+          <t>VIP13包</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2867,7 @@
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>VIP14パック</t>
+          <t>VIP14包</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2950,7 +2924,7 @@
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2985,17 +2959,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3020,7 +2984,7 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>VIP0パック</t>
+          <t>VIP0包</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3077,7 +3041,7 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>VIP1パック</t>
+          <t>VIP1包</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3134,7 +3098,7 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>VIP2パック</t>
+          <t>VIP2包</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3191,7 +3155,7 @@
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>VIP3パック</t>
+          <t>VIP3包</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3248,7 +3212,7 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>VIP4パック</t>
+          <t>VIP4包</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3305,7 +3269,7 @@
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>VIP5パック</t>
+          <t>VIP5包</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3362,7 +3326,7 @@
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>VIP6パック</t>
+          <t>VIP6包</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3419,7 +3383,7 @@
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>VIP7パック</t>
+          <t>VIP7包</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3476,7 +3440,7 @@
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>VIP8パック</t>
+          <t>VIP8包</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3533,7 +3497,7 @@
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>VIP9パック</t>
+          <t>VIP9包</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3590,7 +3554,7 @@
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>VIP10パック</t>
+          <t>VIP10包</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3647,7 +3611,7 @@
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>VIP11パック</t>
+          <t>VIP11包</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3704,7 +3668,7 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>VIP12パック</t>
+          <t>VIP12包</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3761,7 +3725,7 @@
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>VIP13パック</t>
+          <t>VIP13包</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3818,7 +3782,7 @@
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>VIP14パック</t>
+          <t>VIP14包</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3875,7 +3839,7 @@
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3910,17 +3874,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3945,7 +3899,7 @@
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>VIP0パック</t>
+          <t>VIP0包</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4002,7 +3956,7 @@
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>VIP1パック</t>
+          <t>VIP1包</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4059,7 +4013,7 @@
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>VIP2パック</t>
+          <t>VIP2包</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4116,7 +4070,7 @@
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>VIP3パック</t>
+          <t>VIP3包</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4173,7 +4127,7 @@
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>VIP4パック</t>
+          <t>VIP4包</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4230,7 +4184,7 @@
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>VIP5パック</t>
+          <t>VIP5包</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4287,7 +4241,7 @@
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>VIP6パック</t>
+          <t>VIP6包</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4344,7 +4298,7 @@
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>VIP7パック</t>
+          <t>VIP7包</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4401,7 +4355,7 @@
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>VIP8パック</t>
+          <t>VIP8包</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4458,7 +4412,7 @@
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>VIP9パック</t>
+          <t>VIP9包</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4515,7 +4469,7 @@
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>VIP10パック</t>
+          <t>VIP10包</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4572,7 +4526,7 @@
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>VIP11パック</t>
+          <t>VIP11包</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4629,7 +4583,7 @@
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>VIP12パック</t>
+          <t>VIP12包</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4686,7 +4640,7 @@
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>VIP13パック</t>
+          <t>VIP13包</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4743,7 +4697,7 @@
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>VIP14パック</t>
+          <t>VIP14包</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4800,7 +4754,7 @@
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4835,17 +4789,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4870,7 +4814,7 @@
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>VIP0パック</t>
+          <t>VIP0包</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4927,7 +4871,7 @@
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>VIP1パック</t>
+          <t>VIP1包</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4984,7 +4928,7 @@
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>VIP2パック</t>
+          <t>VIP2包</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5041,7 +4985,7 @@
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>VIP3パック</t>
+          <t>VIP3包</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5098,7 +5042,7 @@
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>VIP4パック</t>
+          <t>VIP4包</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5155,7 +5099,7 @@
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>VIP5パック</t>
+          <t>VIP5包</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5212,7 +5156,7 @@
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>VIP6パック</t>
+          <t>VIP6包</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5269,7 +5213,7 @@
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>VIP7パック</t>
+          <t>VIP7包</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5326,7 +5270,7 @@
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>VIP8パック</t>
+          <t>VIP8包</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5383,7 +5327,7 @@
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>VIP9パック</t>
+          <t>VIP9包</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5440,7 +5384,7 @@
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>VIP10パック</t>
+          <t>VIP10包</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5497,7 +5441,7 @@
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>VIP11パック</t>
+          <t>VIP11包</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5554,7 +5498,7 @@
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>VIP12パック</t>
+          <t>VIP12包</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5611,7 +5555,7 @@
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>VIP13パック</t>
+          <t>VIP13包</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5668,7 +5612,7 @@
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>VIP14パック</t>
+          <t>VIP14包</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5725,7 +5669,7 @@
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5760,17 +5704,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5795,7 +5729,7 @@
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>VIP0パック</t>
+          <t>VIP0包</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5852,7 +5786,7 @@
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>VIP1パック</t>
+          <t>VIP1包</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5909,7 +5843,7 @@
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>VIP2パック</t>
+          <t>VIP2包</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5966,7 +5900,7 @@
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>VIP3パック</t>
+          <t>VIP3包</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6023,7 +5957,7 @@
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>VIP4パック</t>
+          <t>VIP4包</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6080,7 +6014,7 @@
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>VIP5パック</t>
+          <t>VIP5包</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6137,7 +6071,7 @@
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>VIP6パック</t>
+          <t>VIP6包</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6194,7 +6128,7 @@
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>VIP7パック</t>
+          <t>VIP7包</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6251,7 +6185,7 @@
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>VIP8パック</t>
+          <t>VIP8包</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6308,7 +6242,7 @@
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>VIP9パック</t>
+          <t>VIP9包</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6365,7 +6299,7 @@
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>VIP10パック</t>
+          <t>VIP10包</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6422,7 +6356,7 @@
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>VIP11パック</t>
+          <t>VIP11包</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6479,7 +6413,7 @@
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>VIP12パック</t>
+          <t>VIP12包</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6536,7 +6470,7 @@
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>VIP13パック</t>
+          <t>VIP13包</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6593,7 +6527,7 @@
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>VIP14パック</t>
+          <t>VIP14包</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6650,7 +6584,7 @@
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6685,17 +6619,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" s="1" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6720,7 +6644,7 @@
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>VIP0パック</t>
+          <t>VIP0包</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6777,7 +6701,7 @@
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>VIP1パック</t>
+          <t>VIP1包</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6834,7 +6758,7 @@
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>VIP2パック</t>
+          <t>VIP2包</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6891,7 +6815,7 @@
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>VIP3パック</t>
+          <t>VIP3包</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6948,7 +6872,7 @@
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>VIP4パック</t>
+          <t>VIP4包</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7005,7 +6929,7 @@
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>VIP5パック</t>
+          <t>VIP5包</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7062,7 +6986,7 @@
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>VIP6パック</t>
+          <t>VIP6包</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7119,7 +7043,7 @@
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>VIP7パック</t>
+          <t>VIP7包</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7176,7 +7100,7 @@
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t>VIP8パック</t>
+          <t>VIP8包</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7233,7 +7157,7 @@
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VIP9パック</t>
+          <t>VIP9包</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7290,7 +7214,7 @@
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VIP10パック</t>
+          <t>VIP10包</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7347,7 +7271,7 @@
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VIP11パック</t>
+          <t>VIP11包</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7404,7 +7328,7 @@
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VIP12パック</t>
+          <t>VIP12包</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7461,7 +7385,7 @@
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VIP13パック</t>
+          <t>VIP13包</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7518,7 +7442,7 @@
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VIP14パック</t>
+          <t>VIP14包</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7575,7 +7499,7 @@
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7610,17 +7534,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" s="1" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7645,7 +7559,7 @@
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VIP0パック</t>
+          <t>VIP0包</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7702,7 +7616,7 @@
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VIP1パック</t>
+          <t>VIP1包</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7759,7 +7673,7 @@
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VIP2パック</t>
+          <t>VIP2包</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7816,7 +7730,7 @@
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VIP3パック</t>
+          <t>VIP3包</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7873,7 +7787,7 @@
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VIP4パック</t>
+          <t>VIP4包</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7930,7 +7844,7 @@
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VIP5パック</t>
+          <t>VIP5包</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7987,7 +7901,7 @@
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VIP6パック</t>
+          <t>VIP6包</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8044,7 +7958,7 @@
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VIP7パック</t>
+          <t>VIP7包</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8101,7 +8015,7 @@
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VIP8パック</t>
+          <t>VIP8包</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8158,7 +8072,7 @@
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VIP9パック</t>
+          <t>VIP9包</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8215,7 +8129,7 @@
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VIP10パック</t>
+          <t>VIP10包</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8272,7 +8186,7 @@
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VIP11パック</t>
+          <t>VIP11包</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8329,7 +8243,7 @@
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VIP12パック</t>
+          <t>VIP12包</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8386,7 +8300,7 @@
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VIP13パック</t>
+          <t>VIP13包</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8443,7 +8357,7 @@
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VIP14パック</t>
+          <t>VIP14包</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8500,7 +8414,7 @@
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8535,17 +8449,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" s="1" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8570,7 +8474,7 @@
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VIP0パック</t>
+          <t>VIP0包</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8627,7 +8531,7 @@
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VIP1パック</t>
+          <t>VIP1包</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8684,7 +8588,7 @@
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VIP2パック</t>
+          <t>VIP2包</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8741,7 +8645,7 @@
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VIP3パック</t>
+          <t>VIP3包</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8798,7 +8702,7 @@
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VIP4パック</t>
+          <t>VIP4包</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8855,7 +8759,7 @@
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VIP5パック</t>
+          <t>VIP5包</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8912,7 +8816,7 @@
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VIP6パック</t>
+          <t>VIP6包</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8969,7 +8873,7 @@
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VIP7パック</t>
+          <t>VIP7包</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9026,7 +8930,7 @@
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VIP8パック</t>
+          <t>VIP8包</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9083,7 +8987,7 @@
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VIP9パック</t>
+          <t>VIP9包</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9140,7 +9044,7 @@
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VIP10パック</t>
+          <t>VIP10包</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9197,7 +9101,7 @@
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VIP11パック</t>
+          <t>VIP11包</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9254,7 +9158,7 @@
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VIP12パック</t>
+          <t>VIP12包</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9311,7 +9215,7 @@
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VIP13パック</t>
+          <t>VIP13包</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9368,7 +9272,7 @@
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VIP14パック</t>
+          <t>VIP14包</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9425,7 +9329,7 @@
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
